--- a/ig/DM-JANVIER-2025/alignement-nuva-atc.xlsx
+++ b/ig/DM-JANVIER-2025/alignement-nuva-atc.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.818</t>
+    <t>1.0.825</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-05</t>
+    <t>2025-01-06</t>
   </si>
   <si>
     <t>Publisher</t>
